--- a/excel_analisis_datos/codigos/c07_visualizacion/datos_visualizacion.xlsx
+++ b/excel_analisis_datos/codigos/c07_visualizacion/datos_visualizacion.xlsx
@@ -488,16 +488,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>99209</v>
+        <v>98600</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>70518</v>
+        <v>71048</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>111650</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>28691</v>
+        <v>27552</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
@@ -510,19 +510,19 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>108101</v>
+        <v>105076</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>71268</v>
+        <v>71415</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>113300</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>36833</v>
+        <v>33661</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.0598</v>
+        <v>0.0302</v>
       </c>
     </row>
     <row r="4">
@@ -532,19 +532,19 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>110162</v>
+        <v>103901</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>72822</v>
+        <v>71193</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>114950</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>37340</v>
+        <v>32708</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.0593</v>
+        <v>-0.001</v>
       </c>
     </row>
     <row r="5">
@@ -554,19 +554,19 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>111625</v>
+        <v>110510</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>73546</v>
+        <v>71608</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>116600</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>38079</v>
+        <v>38902</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.0531</v>
+        <v>0.0425</v>
       </c>
     </row>
     <row r="6">
@@ -576,19 +576,19 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>105803</v>
+        <v>110132</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>72963</v>
+        <v>72919</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>118250</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>32840</v>
+        <v>37213</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.0203</v>
+        <v>0.0197</v>
       </c>
     </row>
     <row r="7">
@@ -598,19 +598,19 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>109380</v>
+        <v>114032</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>72497</v>
+        <v>75885</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>119900</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>36883</v>
+        <v>38147</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.0056</v>
+        <v>0.0367</v>
       </c>
     </row>
     <row r="8">
@@ -620,19 +620,19 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>114098</v>
+        <v>114810</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>75981</v>
+        <v>75238</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>121550</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>38117</v>
+        <v>39572</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.0187</v>
+        <v>0.0251</v>
       </c>
     </row>
     <row r="9">
@@ -642,19 +642,19 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>119242</v>
+        <v>113845</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>75266</v>
+        <v>74207</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>123200</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>43976</v>
+        <v>39638</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.046</v>
+        <v>-0.0014</v>
       </c>
     </row>
     <row r="10">
@@ -664,19 +664,19 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>116454</v>
+        <v>116214</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>75723</v>
+        <v>74224</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>124850</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>40731</v>
+        <v>41990</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.0039</v>
+        <v>0.0018</v>
       </c>
     </row>
     <row r="11">
@@ -686,19 +686,19 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>115806</v>
+        <v>116207</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>77776</v>
+        <v>75581</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>126500</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>38030</v>
+        <v>40626</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-0.0186</v>
+        <v>-0.0152</v>
       </c>
     </row>
     <row r="12">
@@ -708,19 +708,19 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>117298</v>
+        <v>124106</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>76992</v>
+        <v>76053</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>128150</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>40306</v>
+        <v>48053</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-0.0225</v>
+        <v>0.0342</v>
       </c>
     </row>
     <row r="13">
@@ -730,19 +730,19 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>122961</v>
+        <v>122019</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>78124</v>
+        <v>76480</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>129800</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>44837</v>
+        <v>45539</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="14">
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>130115</v>
+        <v>121516</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>79727</v>
+        <v>80789</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>131450</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>50388</v>
+        <v>40727</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.0493</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="15">
@@ -774,19 +774,19 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>127047</v>
+        <v>129466</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>80518</v>
+        <v>80647</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>133100</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>46529</v>
+        <v>48819</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.0083</v>
+        <v>0.0275</v>
       </c>
     </row>
     <row r="16">
@@ -796,19 +796,19 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>125368</v>
+        <v>129358</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>81114</v>
+        <v>82514</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>134750</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>44254</v>
+        <v>46844</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-0.0206</v>
+        <v>0.0106</v>
       </c>
     </row>
     <row r="17">
@@ -818,19 +818,19 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>129231</v>
+        <v>132134</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>80350</v>
+        <v>81286</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>136400</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>48881</v>
+        <v>50848</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-0.0059</v>
+        <v>0.0164</v>
       </c>
     </row>
     <row r="18">
@@ -840,19 +840,19 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>133175</v>
+        <v>133032</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>80193</v>
+        <v>82421</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>138050</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>52982</v>
+        <v>50611</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0.0089</v>
+        <v>0.0078</v>
       </c>
     </row>
     <row r="19">
@@ -862,19 +862,19 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>133978</v>
+        <v>136437</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>82886</v>
+        <v>83402</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>139700</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>51092</v>
+        <v>53035</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-0.0002</v>
+        <v>0.0182</v>
       </c>
     </row>
     <row r="20">
@@ -884,19 +884,19 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>139785</v>
+        <v>134468</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>82999</v>
+        <v>81983</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>141350</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>56786</v>
+        <v>52485</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.0278</v>
+        <v>-0.0113</v>
       </c>
     </row>
     <row r="21">
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>136423</v>
+        <v>142992</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>84351</v>
+        <v>82423</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>143000</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>52072</v>
+        <v>60569</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-0.0114</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="22">
@@ -928,19 +928,19 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>144241</v>
+        <v>143620</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>82973</v>
+        <v>84519</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>144650</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>61268</v>
+        <v>59101</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.0303</v>
+        <v>0.0259</v>
       </c>
     </row>
     <row r="23">
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>146307</v>
+        <v>145680</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>84270</v>
+        <v>87287</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>146300</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>62037</v>
+        <v>58393</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.0303</v>
+        <v>0.0259</v>
       </c>
     </row>
     <row r="24">
@@ -972,19 +972,19 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>144349</v>
+        <v>150516</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>85303</v>
+        <v>87835</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>147950</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>59046</v>
+        <v>62681</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0.0024</v>
+        <v>0.0453</v>
       </c>
     </row>
     <row r="25">
@@ -994,19 +994,19 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>151565</v>
+        <v>146121</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>86300</v>
+        <v>85847</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>149600</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>65265</v>
+        <v>60274</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.0381</v>
+        <v>0.0008</v>
       </c>
     </row>
   </sheetData>
@@ -1188,25 +1188,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>10003</v>
+        <v>25947</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>8380</v>
+        <v>23897</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>15657</v>
+        <v>9055</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>16549</v>
+        <v>15268</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>23546</v>
+        <v>11271</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>29883</v>
+        <v>9899</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>104018</v>
+        <v>95337</v>
       </c>
     </row>
     <row r="3">
@@ -1216,25 +1216,25 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>18121</v>
+        <v>28570</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>12930</v>
+        <v>8725</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>27184</v>
+        <v>23341</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>19475</v>
+        <v>26450</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>14665</v>
+        <v>5833</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>11746</v>
+        <v>8116</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>104121</v>
+        <v>101035</v>
       </c>
     </row>
     <row r="4">
@@ -1244,25 +1244,25 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>23768</v>
+        <v>8223</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>27172</v>
+        <v>11248</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>18586</v>
+        <v>7019</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>12466</v>
+        <v>21953</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>24548</v>
+        <v>15310</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>24782</v>
+        <v>9502</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>131322</v>
+        <v>73255</v>
       </c>
     </row>
     <row r="5">
@@ -1272,25 +1272,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>13426</v>
+        <v>12134</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>25155</v>
+        <v>8353</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>16036</v>
+        <v>16773</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>24545</v>
+        <v>18193</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>14470</v>
+        <v>22485</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>5236</v>
+        <v>10597</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>98868</v>
+        <v>88535</v>
       </c>
     </row>
     <row r="6">
@@ -1300,25 +1300,25 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>11588</v>
+        <v>12727</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>23229</v>
+        <v>14496</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>23444</v>
+        <v>10997</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>16398</v>
+        <v>22797</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>15498</v>
+        <v>13215</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>29382</v>
+        <v>28437</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>119539</v>
+        <v>102669</v>
       </c>
     </row>
     <row r="7">
@@ -1328,25 +1328,25 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>14371</v>
+        <v>5405</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>18590</v>
+        <v>28831</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>16871</v>
+        <v>9108</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>19269</v>
+        <v>9834</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>26709</v>
+        <v>28806</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>26394</v>
+        <v>29077</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>122204</v>
+        <v>111061</v>
       </c>
     </row>
     <row r="8">
@@ -1356,25 +1356,25 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>17058</v>
+        <v>13250</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>11500</v>
+        <v>17928</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>7440</v>
+        <v>10706</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>20398</v>
+        <v>17879</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>6907</v>
+        <v>20617</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>21827</v>
+        <v>7676</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>85130</v>
+        <v>88056</v>
       </c>
     </row>
   </sheetData>
